--- a/VT_Model_SUP_V01.xlsx
+++ b/VT_Model_SUP_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\bbb\MSc_SELECT-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giebe\Downloads\MSc_SELECT_Baseline\MSc_SELECT_Baseline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3B79E5-BAF8-41F8-8ADC-A66F838D3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65697EC2-FEC3-4CCB-91BE-E62C2FE4E460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5112" yWindow="2352" windowWidth="17280" windowHeight="8880" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEC_Comm" sheetId="112" r:id="rId1"/>
@@ -784,7 +784,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="100">
   <si>
     <t>Define Commodities</t>
   </si>
@@ -1075,6 +1075,15 @@
   </si>
   <si>
     <t>ANNUAL</t>
+  </si>
+  <si>
+    <t>URAN</t>
+  </si>
+  <si>
+    <t>Uraniumfuel</t>
+  </si>
+  <si>
+    <t>IMP_URAN</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1819,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="337">
+  <cellStyleXfs count="336">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2105,7 +2114,6 @@
     <xf numFmtId="0" fontId="46" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="46" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="46" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -2227,7 +2235,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="337">
+  <cellStyles count="336">
     <cellStyle name="20% - akcent 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="20% - akcent 1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - akcent 1 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2501,7 +2509,6 @@
     <cellStyle name="Neutralne 6" xfId="271" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
     <cellStyle name="Neutralne 7" xfId="272" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
     <cellStyle name="Neutralne 8" xfId="273" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="274" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
     <cellStyle name="Normal 2" xfId="275" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
     <cellStyle name="Normal 3" xfId="276" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
@@ -2522,49 +2529,49 @@
     <cellStyle name="Obliczenia 6" xfId="291" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
     <cellStyle name="Obliczenia 7" xfId="292" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
     <cellStyle name="Obliczenia 8" xfId="293" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="294" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="Suma" xfId="295" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="Suma 2" xfId="296" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="Suma 3" xfId="297" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="Suma 4" xfId="298" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="Suma 5" xfId="299" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="Suma 6" xfId="300" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="Suma 7" xfId="301" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="Suma 8" xfId="302" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="Tekst objaśnienia" xfId="303" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="Tekst objaśnienia 2" xfId="304" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="Tekst objaśnienia 3" xfId="305" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="Tekst objaśnienia 4" xfId="306" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="Tekst objaśnienia 5" xfId="307" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="Tekst objaśnienia 6" xfId="308" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="Tekst objaśnienia 7" xfId="309" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="Tekst objaśnienia 8" xfId="310" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="Tekst ostrzeżenia" xfId="311" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Tekst ostrzeżenia 2" xfId="312" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="Tekst ostrzeżenia 3" xfId="313" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="Tekst ostrzeżenia 4" xfId="314" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="Tekst ostrzeżenia 5" xfId="315" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="Tekst ostrzeżenia 6" xfId="316" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="Tekst ostrzeżenia 7" xfId="317" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="Tekst ostrzeżenia 8" xfId="318" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="Tytuł" xfId="319" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="Uwaga" xfId="320" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="Uwaga 2" xfId="321" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="Uwaga 3" xfId="322" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="Uwaga 4" xfId="323" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="Uwaga 5" xfId="324" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="Uwaga 6" xfId="325" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Uwaga 7" xfId="326" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="Uwaga 8" xfId="327" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="Złe" xfId="328" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="Złe 2" xfId="329" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="Złe 3" xfId="330" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="Złe 4" xfId="331" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Złe 5" xfId="332" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="Złe 6" xfId="333" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="Złe 7" xfId="334" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="Złe 8" xfId="335" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="已访问的超链接" xfId="336" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Suma" xfId="294" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Suma 2" xfId="295" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Suma 3" xfId="296" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Suma 4" xfId="297" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Suma 5" xfId="298" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Suma 6" xfId="299" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Suma 7" xfId="300" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Suma 8" xfId="301" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Tekst objaśnienia" xfId="302" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Tekst objaśnienia 2" xfId="303" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Tekst objaśnienia 3" xfId="304" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Tekst objaśnienia 4" xfId="305" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Tekst objaśnienia 5" xfId="306" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Tekst objaśnienia 6" xfId="307" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Tekst objaśnienia 7" xfId="308" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Tekst objaśnienia 8" xfId="309" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Tekst ostrzeżenia" xfId="310" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Tekst ostrzeżenia 2" xfId="311" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Tekst ostrzeżenia 3" xfId="312" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Tekst ostrzeżenia 4" xfId="313" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Tekst ostrzeżenia 5" xfId="314" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Tekst ostrzeżenia 6" xfId="315" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Tekst ostrzeżenia 7" xfId="316" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Tekst ostrzeżenia 8" xfId="317" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Tytuł" xfId="318" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Uwaga" xfId="319" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Uwaga 2" xfId="320" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Uwaga 3" xfId="321" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Uwaga 4" xfId="322" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Uwaga 5" xfId="323" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Uwaga 6" xfId="324" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Uwaga 7" xfId="325" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Uwaga 8" xfId="326" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Złe" xfId="327" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Złe 2" xfId="328" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Złe 3" xfId="329" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Złe 4" xfId="330" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Złe 5" xfId="331" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Złe 6" xfId="332" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Złe 7" xfId="333" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Złe 8" xfId="334" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="已访问的超链接" xfId="335" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3069,21 +3076,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:I29"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18">
+    <row r="2" spans="2:9" ht="17.399999999999999">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -3141,7 +3148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="38.25">
+    <row r="6" spans="2:9" ht="39.6">
       <c r="B6" s="37" t="s">
         <v>10</v>
       </c>
@@ -3270,10 +3277,22 @@
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="E12" s="23"/>
+      <c r="B12" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="F12" s="18"/>
+      <c r="G12" s="20" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="13" spans="2:9">
       <c r="F13" s="18"/>
@@ -3321,7 +3340,7 @@
       <c r="C22" s="23"/>
       <c r="E22" s="23"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="13.8" thickBot="1">
       <c r="B24" s="38" t="s">
         <v>18</v>
       </c>
@@ -3359,7 +3378,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="2:5" ht="13.5" thickBot="1">
+    <row r="29" spans="2:5" ht="13.8" thickBot="1">
       <c r="B29" s="22" t="s">
         <v>26</v>
       </c>
@@ -3382,18 +3401,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:J31"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="18" customHeight="1">
@@ -3581,6 +3600,23 @@
       <c r="I11" s="21"/>
       <c r="J11" s="21"/>
     </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
     <row r="15" spans="1:10">
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
@@ -3697,7 +3733,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="13.5" thickBot="1">
+    <row r="31" spans="2:6" ht="13.8" thickBot="1">
       <c r="B31" s="22" t="s">
         <v>66</v>
       </c>
@@ -3721,14 +3757,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T26"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="10" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" customWidth="1"/>
+    <col min="4" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="10" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -3752,7 +3788,7 @@
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
     </row>
-    <row r="2" spans="1:20" ht="18">
+    <row r="2" spans="1:20" ht="17.399999999999999">
       <c r="A2" s="5"/>
       <c r="B2" s="10" t="s">
         <v>68</v>
@@ -3966,6 +4002,17 @@
       <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:20">
+      <c r="B12" t="str">
+        <f>SEC_Processes!D12</f>
+        <v>IMP_URAN</v>
+      </c>
+      <c r="D12" t="str">
+        <f>SEC_Comm!C12</f>
+        <v>URAN</v>
+      </c>
+      <c r="E12">
+        <v>0.5</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="H12" s="14"/>
       <c r="I12" s="5"/>
@@ -4054,21 +4101,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100E800C01780957C4993EAD0B0EDC5E8FF" ma:contentTypeVersion="4" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="56d16bfd38a93d3246b87ec2f908dfef">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="95645557-b925-4e14-b9c3-bb0dccab904e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3e7776de10091f04de0bec4c5ba2ee03" ns2:_="">
     <xsd:import namespace="95645557-b925-4e14-b9c3-bb0dccab904e"/>
@@ -4212,24 +4244,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2354E624-82C6-4C58-B5AA-5F4B4FEE1585}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEC55BD-C1AB-47C6-923C-1E0B74C138B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ADE2FD8-87C7-41E1-A1A0-6DF35B741F42}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4245,4 +4275,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEC55BD-C1AB-47C6-923C-1E0B74C138B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2354E624-82C6-4C58-B5AA-5F4B4FEE1585}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>